--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\NJ\elec\DPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\NJ\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5616A21-C4A9-4C5C-9538-EC1D59284514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA1C325E-D139-4752-84BF-E47FA63316A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1890" windowWidth="14700" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -837,7 +837,7 @@
         <v>90</v>
       </c>
       <c r="C1" s="6">
-        <v>45484</v>
+        <v>46185</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>32</v>
